--- a/WIPO_SEQUENCE_TEMPLATE.xlsx
+++ b/WIPO_SEQUENCE_TEMPLATE.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/53e293430a1fb76d/문서/Javascript Study/hcj-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{3640AB35-25DB-4F55-AFA7-027E59137FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61FC8D93-0425-4A69-BBCF-748237FF3A48}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{3640AB35-25DB-4F55-AFA7-027E59137FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{766FDAA1-8590-467F-A717-A86CE5F7243F}"/>
   <bookViews>
-    <workbookView xWindow="16080" yWindow="5625" windowWidth="51840" windowHeight="21120" xr2:uid="{AC0148A9-0D28-46BE-8AEA-063D32A9730B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{AC0148A9-0D28-46BE-8AEA-063D32A9730B}"/>
   </bookViews>
   <sheets>
-    <sheet name="서열정보" sheetId="1" r:id="rId1"/>
+    <sheet name="Sequence" sheetId="1" r:id="rId1"/>
     <sheet name="선택지" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
@@ -52,14 +52,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>종류</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>유래 생물</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DNA</t>
   </si>
   <si>
@@ -117,31 +109,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>세부종류</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>서열번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>비고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ATGCAATATT</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>서열(U는 T로 작성)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예시입니다. 삭제하셔도 됩니다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Homo sapiens</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEQ NO.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Molecule type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qualifier molecule type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sequence / Residues (type "U" for "T")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Organism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remarks</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Example</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -324,6 +324,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -627,31 +631,31 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="3"/>
-    <col min="3" max="3" width="13.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.75" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.75" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.75" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>2</v>
-      </c>
       <c r="C1" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -660,19 +664,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>25</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -706,10 +710,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -717,51 +721,51 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/WIPO_SEQUENCE_TEMPLATE.xlsx
+++ b/WIPO_SEQUENCE_TEMPLATE.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/53e293430a1fb76d/문서/Javascript Study/hcj-main/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/53e293430a1fb76d/문서/Coding/WIPO_SEQUENCE_SOCKS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{3640AB35-25DB-4F55-AFA7-027E59137FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{766FDAA1-8590-467F-A717-A86CE5F7243F}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{3640AB35-25DB-4F55-AFA7-027E59137FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB5BB480-DB00-4B5B-9619-126FCDFC9DE1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{AC0148A9-0D28-46BE-8AEA-063D32A9730B}"/>
+    <workbookView xWindow="1920" yWindow="1410" windowWidth="17040" windowHeight="11835" xr2:uid="{AC0148A9-0D28-46BE-8AEA-063D32A9730B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sequence" sheetId="1" r:id="rId1"/>
@@ -52,9 +52,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DNA</t>
-  </si>
-  <si>
     <t>RNA</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -63,9 +60,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>genomic DNA</t>
-  </si>
-  <si>
     <t>unassigned DNA</t>
   </si>
   <si>
@@ -129,10 +123,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Sequence / Residues (type "U" for "T")</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Organism</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -143,6 +133,16 @@
   <si>
     <t>Example</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sequence / Residues (type "T" for "U")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RNA</t>
+  </si>
+  <si>
+    <t>genomic RNA</t>
   </si>
 </sst>
 </file>
@@ -324,10 +324,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -640,22 +636,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="F1" s="10" t="s">
         <v>21</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -664,19 +660,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -710,10 +706,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -721,51 +717,51 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
